--- a/output/pdf_financials_xlsx/EFF.xlsx
+++ b/output/pdf_financials_xlsx/EFF.xlsx
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001885</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.128467</v>
+        <v>-1.130352</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-4.642636</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.128467</v>
+        <v>-1.130352</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.642636</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-59865.62334217507</v>
+        <v>-59965.62334217507</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2414,43 +2414,43 @@
         <v>0.956893</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.470366</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.123161</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.076058</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.050233</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.043398</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.050378</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.034137</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.123804</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.205713</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.049756</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.066597</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.189192</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.3352</v>
       </c>
     </row>
     <row r="35">
@@ -2524,43 +2524,43 @@
         <v>0.956893</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.470366</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.123161</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.076058</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.050233</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.043398</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.050378</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.034137</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.123804</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.205713</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.049756</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.066597</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.189192</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.3352</v>
       </c>
     </row>
     <row r="37">
@@ -3184,43 +3184,43 @@
         <v>0.078371</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.584741</v>
+        <v>0.114375</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.153231</v>
+        <v>0.03007</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.09672600000000001</v>
+        <v>0.020668</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.07012500000000001</v>
+        <v>0.019892</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.044802</v>
+        <v>0.001404</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.057782</v>
+        <v>0.007404</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.07439900000000001</v>
+        <v>0.040262</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.149972</v>
+        <v>0.026168</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.342209</v>
+        <v>0.136496</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.180865</v>
+        <v>0.131109</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.126368</v>
+        <v>0.059771</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.207547</v>
+        <v>0.018355</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.353871</v>
+        <v>0.018671</v>
       </c>
     </row>
     <row r="49">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10696,7 +10696,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -16212,7 +16216,11 @@
           <t>Decrease in reclamation deposit</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16580,7 +16588,11 @@
           <t>Increase in reclamation deposit</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -26414,7 +26426,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">

--- a/output/pdf_financials_xlsx/EFF.xlsx
+++ b/output/pdf_financials_xlsx/EFF.xlsx
@@ -1339,7 +1339,7 @@
         <v>0.137534</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.136373</v>
+        <v>0.104474</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2267,7 +2267,7 @@
         <v>-12.18768470854708</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-2.937404526221741</v>
+        <v>-2.250316415071093</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -24490,7 +24490,11 @@
           <t>Income tax recovery (expense) (Note 6)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -25756,7 +25760,11 @@
           <t>Deferred income tax recovery (Note 4)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
